--- a/artfynd/A 22052-2020 artfynd.xlsx
+++ b/artfynd/A 22052-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119798118</v>
+        <v>119798119</v>
       </c>
       <c r="B2" t="n">
-        <v>78526</v>
+        <v>74577</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6426</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>513829</v>
+        <v>513830</v>
       </c>
       <c r="R2" t="n">
-        <v>6790986</v>
+        <v>6790995</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -765,12 +765,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119798119</v>
+        <v>119798116</v>
       </c>
       <c r="B4" t="n">
-        <v>74577</v>
+        <v>78526</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>513830</v>
+        <v>513836</v>
       </c>
       <c r="R4" t="n">
-        <v>6790995</v>
+        <v>6790994</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119798116</v>
+        <v>119798118</v>
       </c>
       <c r="B5" t="n">
         <v>78526</v>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>513836</v>
+        <v>513829</v>
       </c>
       <c r="R5" t="n">
-        <v>6790994</v>
+        <v>6790986</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,12 +1071,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 22052-2020 artfynd.xlsx
+++ b/artfynd/A 22052-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119798119</v>
+        <v>119797981</v>
       </c>
       <c r="B2" t="n">
-        <v>74577</v>
+        <v>78526</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Jässelåsen, Jässelåsen, Dlr</t>
+          <t>Lill-Björntjärnen, Lill-Björntjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>513830</v>
+        <v>513729</v>
       </c>
       <c r="R2" t="n">
-        <v>6790995</v>
+        <v>6791056</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -765,19 +765,19 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119797981</v>
+        <v>119798116</v>
       </c>
       <c r="B3" t="n">
         <v>78526</v>
@@ -813,14 +813,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lill-Björntjärnen, Lill-Björntjärnen, Dlr</t>
+          <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>513729</v>
+        <v>513836</v>
       </c>
       <c r="R3" t="n">
-        <v>6791056</v>
+        <v>6790994</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,19 +867,19 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119798116</v>
+        <v>119798118</v>
       </c>
       <c r="B4" t="n">
         <v>78526</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>513836</v>
+        <v>513829</v>
       </c>
       <c r="R4" t="n">
-        <v>6790994</v>
+        <v>6790986</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,22 +969,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119798118</v>
+        <v>119798119</v>
       </c>
       <c r="B5" t="n">
-        <v>78526</v>
+        <v>74577</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6426</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>513829</v>
+        <v>513830</v>
       </c>
       <c r="R5" t="n">
-        <v>6790986</v>
+        <v>6790995</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,12 +1071,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 22052-2020 artfynd.xlsx
+++ b/artfynd/A 22052-2020 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119797981</v>
+        <v>119798118</v>
       </c>
       <c r="B2" t="n">
         <v>78526</v>
@@ -711,14 +711,14 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lill-Björntjärnen, Lill-Björntjärnen, Dlr</t>
+          <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>513729</v>
+        <v>513829</v>
       </c>
       <c r="R2" t="n">
-        <v>6791056</v>
+        <v>6790986</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119798118</v>
+        <v>119797981</v>
       </c>
       <c r="B4" t="n">
         <v>78526</v>
@@ -915,14 +915,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Jässelåsen, Jässelåsen, Dlr</t>
+          <t>Lill-Björntjärnen, Lill-Björntjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>513829</v>
+        <v>513729</v>
       </c>
       <c r="R4" t="n">
-        <v>6790986</v>
+        <v>6791056</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 22052-2020 artfynd.xlsx
+++ b/artfynd/A 22052-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>119798118</v>
       </c>
       <c r="B2" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119798116</v>
+        <v>119797981</v>
       </c>
       <c r="B3" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,14 +813,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Jässelåsen, Jässelåsen, Dlr</t>
+          <t>Lill-Björntjärnen, Lill-Björntjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>513836</v>
+        <v>513729</v>
       </c>
       <c r="R3" t="n">
-        <v>6790994</v>
+        <v>6791056</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,22 +867,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119797981</v>
+        <v>119798119</v>
       </c>
       <c r="B4" t="n">
-        <v>78526</v>
+        <v>74593</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,38 +891,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6426</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lill-Björntjärnen, Lill-Björntjärnen, Dlr</t>
+          <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>513729</v>
+        <v>513830</v>
       </c>
       <c r="R4" t="n">
-        <v>6791056</v>
+        <v>6790995</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,22 +969,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119798119</v>
+        <v>119798116</v>
       </c>
       <c r="B5" t="n">
-        <v>74577</v>
+        <v>78542</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>513830</v>
+        <v>513836</v>
       </c>
       <c r="R5" t="n">
-        <v>6790995</v>
+        <v>6790994</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 22052-2020 artfynd.xlsx
+++ b/artfynd/A 22052-2020 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119798118</v>
+        <v>119797981</v>
       </c>
       <c r="B2" t="n">
         <v>78542</v>
@@ -711,14 +711,14 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Jässelåsen, Jässelåsen, Dlr</t>
+          <t>Lill-Björntjärnen, Lill-Björntjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>513829</v>
+        <v>513729</v>
       </c>
       <c r="R2" t="n">
-        <v>6790986</v>
+        <v>6791056</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119797981</v>
+        <v>119798118</v>
       </c>
       <c r="B3" t="n">
         <v>78542</v>
@@ -813,14 +813,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lill-Björntjärnen, Lill-Björntjärnen, Dlr</t>
+          <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>513729</v>
+        <v>513829</v>
       </c>
       <c r="R3" t="n">
-        <v>6791056</v>
+        <v>6790986</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 22052-2020 artfynd.xlsx
+++ b/artfynd/A 22052-2020 artfynd.xlsx
@@ -1086,7 +1086,7 @@
         <v>122031057</v>
       </c>
       <c r="B6" t="n">
-        <v>79263</v>
+        <v>79264</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 22052-2020 artfynd.xlsx
+++ b/artfynd/A 22052-2020 artfynd.xlsx
@@ -1086,7 +1086,7 @@
         <v>122031057</v>
       </c>
       <c r="B6" t="n">
-        <v>79264</v>
+        <v>79269</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
